--- a/Gas data 2.0/118-S.xlsx
+++ b/Gas data 2.0/118-S.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\19065963\Downloads\Emissions_data\Gas data 2.0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F4B3484-7ACD-4054-B9B2-7C6B38B6EF4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56443F60-0789-4220-968F-747EABE0BCAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-25575" yWindow="3330" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2491,15 +2491,15 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>428625</xdr:colOff>
-      <xdr:row>5</xdr:row>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>752475</xdr:colOff>
+      <xdr:row>4</xdr:row>
       <xdr:rowOff>138112</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>390525</xdr:colOff>
-      <xdr:row>20</xdr:row>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>180975</xdr:colOff>
+      <xdr:row>19</xdr:row>
       <xdr:rowOff>23812</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
